--- a/Data/Cleaned/Aster Retail Holdings Pivot.xlsx
+++ b/Data/Cleaned/Aster Retail Holdings Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Infotact-Solution-Project-1\Data\Cleaned\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28757D0-EC97-4E68-8C2F-3EB94FD57437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD446D4-3908-4599-B1BD-1B2B77EBDD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId3"/>
+    <pivotCache cacheId="16" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="70">
   <si>
     <t>order_id</t>
   </si>
@@ -240,6 +240,12 @@
   <si>
     <t>Electronics (UK)</t>
   </si>
+  <si>
+    <t>Dark Red</t>
+  </si>
+  <si>
+    <t>Lowest</t>
+  </si>
 </sst>
 </file>
 
@@ -268,7 +274,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,8 +287,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -314,11 +326,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -328,16 +349,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="93">
+  <dxfs count="59">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4B4B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF4B4B"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -589,6 +656,146 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -696,497 +903,13 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF4B4B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1196,6 +919,3388 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Aster Retail Holdings Pivot.xlsx]EDA!PivotTable7</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales by Category</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>EDA!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>EDA!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Accessories</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Clothing</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EDA!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>280575</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>209136</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>242079</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6A86-4B4B-B6C1-AF247C772133}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1005534224"/>
+        <c:axId val="1005534704"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1005534224"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1005534704"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1005534704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1005534224"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Aster Retail Holdings Pivot.xlsx]EDA!PivotTable8</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Monthly</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Trends</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>EDA!$J$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>EDA!$I$4:$I$16</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>Jan</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Feb</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mar</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Apr</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jun</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Jul</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Aug</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sep</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Oct</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Nov</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Dec</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EDA!$J$4:$J$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>54020</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>61316</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>54013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>65379</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>64927</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>64948</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>61130</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>96241</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>66313</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>51339</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>46723</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45441</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1410-4711-AE74-5EC2BE24B270}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="270628064"/>
+        <c:axId val="270628544"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="270628064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="270628544"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="270628544"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="270628064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Aster Retail Holdings Pivot.xlsx]EDA!PivotTable9</c:name>
+    <c:fmtId val="1"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Country-wise</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> Sales</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>EDA!$O$3:$O$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Accessories</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>EDA!$N$5:$N$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>UK</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>USA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EDA!$O$5:$O$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>37384</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>56126</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39300</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>49756</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47417</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50592</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-02AE-4A06-9328-E0889E22ADE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>EDA!$P$3:$P$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Clothing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>EDA!$N$5:$N$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>UK</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>USA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EDA!$P$5:$P$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>31291</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>49508</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>29578</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>33187</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>33206</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>32366</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-02AE-4A06-9328-E0889E22ADE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>EDA!$Q$3:$Q$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>EDA!$N$5:$N$11</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Australia</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Canada</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>UK</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>USA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>EDA!$Q$5:$Q$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>45992</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32594</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>34912</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>45052</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>27826</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>55703</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-02AE-4A06-9328-E0889E22ADE1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="997404576"/>
+        <c:axId val="997405056"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="997404576"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="997405056"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="997405056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="997404576"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>975360</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5077F365-F614-7FCC-182D-E0E0479D9687}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>601980</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2762D24-3A20-9E80-DADD-F84E7767E9C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>163830</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A9CBE77F-848C-1D7D-18B3-9B7A2384A6E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8925,554 +12030,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A3E1BC63-E380-434D-8B43-7486353E4CBC}" name="PivotTable9" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Country" colHeaderCaption="Category">
-  <location ref="I3:M11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item x="2"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="262">
-        <item x="6"/>
-        <item x="252"/>
-        <item x="50"/>
-        <item x="137"/>
-        <item x="199"/>
-        <item x="131"/>
-        <item x="179"/>
-        <item x="128"/>
-        <item x="43"/>
-        <item x="70"/>
-        <item x="100"/>
-        <item x="173"/>
-        <item x="255"/>
-        <item x="51"/>
-        <item x="109"/>
-        <item x="171"/>
-        <item x="240"/>
-        <item x="41"/>
-        <item x="116"/>
-        <item x="249"/>
-        <item x="181"/>
-        <item x="138"/>
-        <item x="226"/>
-        <item x="60"/>
-        <item x="208"/>
-        <item x="75"/>
-        <item x="94"/>
-        <item x="98"/>
-        <item x="35"/>
-        <item x="182"/>
-        <item x="121"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="187"/>
-        <item x="29"/>
-        <item x="12"/>
-        <item x="204"/>
-        <item x="114"/>
-        <item x="117"/>
-        <item x="175"/>
-        <item x="245"/>
-        <item x="118"/>
-        <item x="4"/>
-        <item x="238"/>
-        <item x="105"/>
-        <item x="195"/>
-        <item x="65"/>
-        <item x="217"/>
-        <item x="259"/>
-        <item x="258"/>
-        <item x="18"/>
-        <item x="148"/>
-        <item x="209"/>
-        <item x="242"/>
-        <item x="129"/>
-        <item x="86"/>
-        <item x="22"/>
-        <item x="203"/>
-        <item x="167"/>
-        <item x="228"/>
-        <item x="188"/>
-        <item x="201"/>
-        <item x="106"/>
-        <item x="202"/>
-        <item x="25"/>
-        <item x="13"/>
-        <item x="78"/>
-        <item x="154"/>
-        <item x="239"/>
-        <item x="80"/>
-        <item x="30"/>
-        <item x="71"/>
-        <item x="9"/>
-        <item x="197"/>
-        <item x="93"/>
-        <item x="36"/>
-        <item x="62"/>
-        <item x="218"/>
-        <item x="82"/>
-        <item x="227"/>
-        <item x="247"/>
-        <item x="119"/>
-        <item x="232"/>
-        <item x="214"/>
-        <item x="250"/>
-        <item x="85"/>
-        <item x="81"/>
-        <item x="163"/>
-        <item x="11"/>
-        <item x="192"/>
-        <item x="243"/>
-        <item x="5"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="146"/>
-        <item x="123"/>
-        <item x="164"/>
-        <item x="140"/>
-        <item x="229"/>
-        <item x="133"/>
-        <item x="174"/>
-        <item x="24"/>
-        <item x="143"/>
-        <item x="127"/>
-        <item x="48"/>
-        <item x="158"/>
-        <item x="166"/>
-        <item x="95"/>
-        <item x="57"/>
-        <item x="23"/>
-        <item x="237"/>
-        <item x="178"/>
-        <item x="55"/>
-        <item x="210"/>
-        <item x="59"/>
-        <item x="90"/>
-        <item x="139"/>
-        <item x="225"/>
-        <item x="153"/>
-        <item x="66"/>
-        <item x="134"/>
-        <item x="157"/>
-        <item x="132"/>
-        <item x="92"/>
-        <item x="58"/>
-        <item x="61"/>
-        <item x="46"/>
-        <item x="120"/>
-        <item x="152"/>
-        <item x="99"/>
-        <item x="230"/>
-        <item x="26"/>
-        <item x="122"/>
-        <item x="108"/>
-        <item x="16"/>
-        <item x="96"/>
-        <item x="161"/>
-        <item x="17"/>
-        <item x="136"/>
-        <item x="235"/>
-        <item x="83"/>
-        <item x="190"/>
-        <item x="184"/>
-        <item x="155"/>
-        <item x="169"/>
-        <item x="32"/>
-        <item x="205"/>
-        <item x="113"/>
-        <item x="216"/>
-        <item x="185"/>
-        <item x="168"/>
-        <item x="244"/>
-        <item x="76"/>
-        <item x="251"/>
-        <item x="87"/>
-        <item x="33"/>
-        <item x="28"/>
-        <item x="124"/>
-        <item x="39"/>
-        <item x="47"/>
-        <item x="97"/>
-        <item x="219"/>
-        <item x="91"/>
-        <item x="183"/>
-        <item x="170"/>
-        <item x="130"/>
-        <item x="256"/>
-        <item x="110"/>
-        <item x="125"/>
-        <item x="212"/>
-        <item x="14"/>
-        <item x="31"/>
-        <item x="7"/>
-        <item x="186"/>
-        <item x="74"/>
-        <item x="44"/>
-        <item x="21"/>
-        <item x="89"/>
-        <item x="42"/>
-        <item x="191"/>
-        <item x="149"/>
-        <item x="73"/>
-        <item x="38"/>
-        <item x="215"/>
-        <item x="189"/>
-        <item x="49"/>
-        <item x="54"/>
-        <item x="176"/>
-        <item x="206"/>
-        <item x="231"/>
-        <item x="79"/>
-        <item x="111"/>
-        <item x="193"/>
-        <item x="63"/>
-        <item x="15"/>
-        <item x="104"/>
-        <item x="254"/>
-        <item x="150"/>
-        <item x="88"/>
-        <item x="19"/>
-        <item x="1"/>
-        <item x="52"/>
-        <item x="234"/>
-        <item x="194"/>
-        <item x="135"/>
-        <item x="112"/>
-        <item x="27"/>
-        <item x="103"/>
-        <item x="207"/>
-        <item x="37"/>
-        <item x="8"/>
-        <item x="147"/>
-        <item x="220"/>
-        <item x="257"/>
-        <item x="145"/>
-        <item x="72"/>
-        <item x="165"/>
-        <item x="172"/>
-        <item x="211"/>
-        <item x="224"/>
-        <item x="198"/>
-        <item x="162"/>
-        <item x="213"/>
-        <item x="84"/>
-        <item x="196"/>
-        <item x="180"/>
-        <item x="159"/>
-        <item x="0"/>
-        <item x="248"/>
-        <item x="260"/>
-        <item x="142"/>
-        <item x="64"/>
-        <item x="45"/>
-        <item x="241"/>
-        <item x="144"/>
-        <item x="67"/>
-        <item x="126"/>
-        <item x="222"/>
-        <item x="53"/>
-        <item x="77"/>
-        <item x="221"/>
-        <item x="115"/>
-        <item x="56"/>
-        <item x="34"/>
-        <item x="107"/>
-        <item x="156"/>
-        <item x="223"/>
-        <item x="160"/>
-        <item x="20"/>
-        <item x="246"/>
-        <item x="200"/>
-        <item x="236"/>
-        <item x="101"/>
-        <item x="40"/>
-        <item x="177"/>
-        <item x="233"/>
-        <item x="102"/>
-        <item x="253"/>
-        <item x="151"/>
-        <item x="141"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="3"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Total Sales" fld="11" baseField="0" baseItem="0"/>
-  </dataFields>
-  <conditionalFormats count="7">
-    <conditionalFormat priority="21">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="20">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="19">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="18">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="17">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="16">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="15">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="3">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-            <reference field="4" count="3" selected="0">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-            </reference>
-            <reference field="10" count="6">
-              <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-  </conditionalFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81698782-36EE-4C19-8937-7E2BADA10105}" name="PivotTable8" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Months(2022)">
-  <location ref="E3:F16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{81698782-36EE-4C19-8937-7E2BADA10105}" name="PivotTable8" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Months(2022)">
+  <location ref="I3:J16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -10196,8 +12755,8 @@
   <dataFields count="1">
     <dataField name="Total" fld="11" baseField="13" baseItem="1"/>
   </dataFields>
-  <conditionalFormats count="3">
-    <conditionalFormat priority="27">
+  <conditionalFormats count="4">
+    <conditionalFormat priority="32">
       <pivotAreas count="12">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -10321,7 +12880,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="26">
+    <conditionalFormat priority="31">
       <pivotAreas count="12">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -10445,7 +13004,7 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="25">
+    <conditionalFormat priority="30">
       <pivotAreas count="12">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
@@ -10569,7 +13128,32 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
+    <conditionalFormat priority="5">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="13" count="1">
+              <x v="12"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
   </conditionalFormats>
+  <chartFormats count="1">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -10582,8 +13166,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61336906-66C7-41BA-A421-B79737C8D957}" name="PivotTable7" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Categoires">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{61336906-66C7-41BA-A421-B79737C8D957}" name="PivotTable7" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Categoires">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -11286,6 +13870,637 @@
   <dataFields count="1">
     <dataField name="Total" fld="11" baseField="4" baseItem="0"/>
   </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A3E1BC63-E380-434D-8B43-7486353E4CBC}" name="PivotTable9" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Country" colHeaderCaption="Category">
+  <location ref="N3:R11" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="262">
+        <item x="6"/>
+        <item x="252"/>
+        <item x="50"/>
+        <item x="137"/>
+        <item x="199"/>
+        <item x="131"/>
+        <item x="179"/>
+        <item x="128"/>
+        <item x="43"/>
+        <item x="70"/>
+        <item x="100"/>
+        <item x="173"/>
+        <item x="255"/>
+        <item x="51"/>
+        <item x="109"/>
+        <item x="171"/>
+        <item x="240"/>
+        <item x="41"/>
+        <item x="116"/>
+        <item x="249"/>
+        <item x="181"/>
+        <item x="138"/>
+        <item x="226"/>
+        <item x="60"/>
+        <item x="208"/>
+        <item x="75"/>
+        <item x="94"/>
+        <item x="98"/>
+        <item x="35"/>
+        <item x="182"/>
+        <item x="121"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="187"/>
+        <item x="29"/>
+        <item x="12"/>
+        <item x="204"/>
+        <item x="114"/>
+        <item x="117"/>
+        <item x="175"/>
+        <item x="245"/>
+        <item x="118"/>
+        <item x="4"/>
+        <item x="238"/>
+        <item x="105"/>
+        <item x="195"/>
+        <item x="65"/>
+        <item x="217"/>
+        <item x="259"/>
+        <item x="258"/>
+        <item x="18"/>
+        <item x="148"/>
+        <item x="209"/>
+        <item x="242"/>
+        <item x="129"/>
+        <item x="86"/>
+        <item x="22"/>
+        <item x="203"/>
+        <item x="167"/>
+        <item x="228"/>
+        <item x="188"/>
+        <item x="201"/>
+        <item x="106"/>
+        <item x="202"/>
+        <item x="25"/>
+        <item x="13"/>
+        <item x="78"/>
+        <item x="154"/>
+        <item x="239"/>
+        <item x="80"/>
+        <item x="30"/>
+        <item x="71"/>
+        <item x="9"/>
+        <item x="197"/>
+        <item x="93"/>
+        <item x="36"/>
+        <item x="62"/>
+        <item x="218"/>
+        <item x="82"/>
+        <item x="227"/>
+        <item x="247"/>
+        <item x="119"/>
+        <item x="232"/>
+        <item x="214"/>
+        <item x="250"/>
+        <item x="85"/>
+        <item x="81"/>
+        <item x="163"/>
+        <item x="11"/>
+        <item x="192"/>
+        <item x="243"/>
+        <item x="5"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="146"/>
+        <item x="123"/>
+        <item x="164"/>
+        <item x="140"/>
+        <item x="229"/>
+        <item x="133"/>
+        <item x="174"/>
+        <item x="24"/>
+        <item x="143"/>
+        <item x="127"/>
+        <item x="48"/>
+        <item x="158"/>
+        <item x="166"/>
+        <item x="95"/>
+        <item x="57"/>
+        <item x="23"/>
+        <item x="237"/>
+        <item x="178"/>
+        <item x="55"/>
+        <item x="210"/>
+        <item x="59"/>
+        <item x="90"/>
+        <item x="139"/>
+        <item x="225"/>
+        <item x="153"/>
+        <item x="66"/>
+        <item x="134"/>
+        <item x="157"/>
+        <item x="132"/>
+        <item x="92"/>
+        <item x="58"/>
+        <item x="61"/>
+        <item x="46"/>
+        <item x="120"/>
+        <item x="152"/>
+        <item x="99"/>
+        <item x="230"/>
+        <item x="26"/>
+        <item x="122"/>
+        <item x="108"/>
+        <item x="16"/>
+        <item x="96"/>
+        <item x="161"/>
+        <item x="17"/>
+        <item x="136"/>
+        <item x="235"/>
+        <item x="83"/>
+        <item x="190"/>
+        <item x="184"/>
+        <item x="155"/>
+        <item x="169"/>
+        <item x="32"/>
+        <item x="205"/>
+        <item x="113"/>
+        <item x="216"/>
+        <item x="185"/>
+        <item x="168"/>
+        <item x="244"/>
+        <item x="76"/>
+        <item x="251"/>
+        <item x="87"/>
+        <item x="33"/>
+        <item x="28"/>
+        <item x="124"/>
+        <item x="39"/>
+        <item x="47"/>
+        <item x="97"/>
+        <item x="219"/>
+        <item x="91"/>
+        <item x="183"/>
+        <item x="170"/>
+        <item x="130"/>
+        <item x="256"/>
+        <item x="110"/>
+        <item x="125"/>
+        <item x="212"/>
+        <item x="14"/>
+        <item x="31"/>
+        <item x="7"/>
+        <item x="186"/>
+        <item x="74"/>
+        <item x="44"/>
+        <item x="21"/>
+        <item x="89"/>
+        <item x="42"/>
+        <item x="191"/>
+        <item x="149"/>
+        <item x="73"/>
+        <item x="38"/>
+        <item x="215"/>
+        <item x="189"/>
+        <item x="49"/>
+        <item x="54"/>
+        <item x="176"/>
+        <item x="206"/>
+        <item x="231"/>
+        <item x="79"/>
+        <item x="111"/>
+        <item x="193"/>
+        <item x="63"/>
+        <item x="15"/>
+        <item x="104"/>
+        <item x="254"/>
+        <item x="150"/>
+        <item x="88"/>
+        <item x="19"/>
+        <item x="1"/>
+        <item x="52"/>
+        <item x="234"/>
+        <item x="194"/>
+        <item x="135"/>
+        <item x="112"/>
+        <item x="27"/>
+        <item x="103"/>
+        <item x="207"/>
+        <item x="37"/>
+        <item x="8"/>
+        <item x="147"/>
+        <item x="220"/>
+        <item x="257"/>
+        <item x="145"/>
+        <item x="72"/>
+        <item x="165"/>
+        <item x="172"/>
+        <item x="211"/>
+        <item x="224"/>
+        <item x="198"/>
+        <item x="162"/>
+        <item x="213"/>
+        <item x="84"/>
+        <item x="196"/>
+        <item x="180"/>
+        <item x="159"/>
+        <item x="0"/>
+        <item x="248"/>
+        <item x="260"/>
+        <item x="142"/>
+        <item x="64"/>
+        <item x="45"/>
+        <item x="241"/>
+        <item x="144"/>
+        <item x="67"/>
+        <item x="126"/>
+        <item x="222"/>
+        <item x="53"/>
+        <item x="77"/>
+        <item x="221"/>
+        <item x="115"/>
+        <item x="56"/>
+        <item x="34"/>
+        <item x="107"/>
+        <item x="156"/>
+        <item x="223"/>
+        <item x="160"/>
+        <item x="20"/>
+        <item x="246"/>
+        <item x="200"/>
+        <item x="236"/>
+        <item x="101"/>
+        <item x="40"/>
+        <item x="177"/>
+        <item x="233"/>
+        <item x="102"/>
+        <item x="253"/>
+        <item x="151"/>
+        <item x="141"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="10"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total Sales" fld="11" baseField="0" baseItem="0"/>
+  </dataFields>
+  <conditionalFormats count="7">
+    <conditionalFormat priority="26">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="25">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="24">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="23">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="22">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="21">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="20">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="3">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+            <reference field="4" count="3" selected="0">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+            </reference>
+            <reference field="10" count="6">
+              <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <chartFormats count="6">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -30634,526 +33849,574 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60380152-6984-427D-9320-B69221E379C3}">
-  <dimension ref="A2:M21"/>
+  <dimension ref="A2:R22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="12.109375" customWidth="1"/>
     <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.21875" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" customWidth="1"/>
     <col min="11" max="11" width="15.109375" customWidth="1"/>
     <col min="12" max="12" width="14.109375" customWidth="1"/>
     <col min="13" max="13" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="15" max="15" width="16.88671875" customWidth="1"/>
+    <col min="16" max="16" width="20.88671875" customWidth="1"/>
+    <col min="17" max="17" width="17.88671875" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="E2" s="7" t="s">
+      <c r="B2" s="6"/>
+      <c r="I2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="6"/>
+      <c r="N2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4">
         <v>280575</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="5">
+      <c r="J4" s="9">
         <v>54020</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J4" t="s">
+      <c r="O4" t="s">
         <v>20</v>
       </c>
-      <c r="K4" t="s">
+      <c r="P4" t="s">
         <v>24</v>
       </c>
-      <c r="L4" t="s">
+      <c r="Q4" t="s">
         <v>13</v>
       </c>
-      <c r="M4" t="s">
+      <c r="R4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5">
         <v>209136</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="5">
+      <c r="J5" s="9">
         <v>61316</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="N5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="5">
+      <c r="O5">
         <v>37384</v>
       </c>
-      <c r="K5" s="5">
+      <c r="P5">
         <v>31291</v>
       </c>
-      <c r="L5" s="5">
+      <c r="Q5">
         <v>45992</v>
       </c>
-      <c r="M5" s="5">
+      <c r="R5">
         <v>114667</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6">
         <v>242079</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="I6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="5">
+      <c r="J6" s="9">
         <v>54013</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="5">
+      <c r="O6">
         <v>56126</v>
       </c>
-      <c r="K6" s="5">
+      <c r="P6">
         <v>49508</v>
       </c>
-      <c r="L6" s="5">
+      <c r="Q6">
         <v>32594</v>
       </c>
-      <c r="M6" s="5">
+      <c r="R6">
         <v>138228</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7">
         <v>731790</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="5">
+      <c r="J7" s="9">
         <v>65379</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="N7" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="5">
+      <c r="O7">
         <v>39300</v>
       </c>
-      <c r="K7" s="5">
+      <c r="P7">
         <v>29578</v>
       </c>
-      <c r="L7" s="5">
+      <c r="Q7">
         <v>34912</v>
       </c>
-      <c r="M7" s="5">
+      <c r="R7">
         <v>103790</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E8" s="4" t="s">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="5">
+      <c r="J8" s="9">
         <v>64927</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="N8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J8" s="5">
+      <c r="O8">
         <v>49756</v>
       </c>
-      <c r="K8" s="5">
+      <c r="P8">
         <v>33187</v>
       </c>
-      <c r="L8" s="5">
+      <c r="Q8">
         <v>45052</v>
       </c>
-      <c r="M8" s="5">
+      <c r="R8">
         <v>127995</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E9" s="4" t="s">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I9" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="5">
+      <c r="J9" s="9">
         <v>64948</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="N9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="5">
+      <c r="O9">
         <v>47417</v>
       </c>
-      <c r="K9" s="5">
+      <c r="P9">
         <v>33206</v>
       </c>
-      <c r="L9" s="5">
+      <c r="Q9">
         <v>27826</v>
       </c>
-      <c r="M9" s="5">
+      <c r="R9">
         <v>108449</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E10" s="4" t="s">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="7">
+        <v>731790</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F10" s="5">
+      <c r="J10" s="9">
         <v>61130</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="N10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="5">
+      <c r="O10">
         <v>50592</v>
       </c>
-      <c r="K10" s="5">
+      <c r="P10">
         <v>32366</v>
       </c>
-      <c r="L10" s="5">
+      <c r="Q10">
         <v>55703</v>
       </c>
-      <c r="M10" s="5">
+      <c r="R10">
         <v>138661</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E11" s="4" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I11" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="5">
+      <c r="J11" s="9">
         <v>96241</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="N11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="5">
+      <c r="O11">
         <v>280575</v>
       </c>
-      <c r="K11" s="5">
+      <c r="P11">
         <v>209136</v>
       </c>
-      <c r="L11" s="5">
+      <c r="Q11">
         <v>242079</v>
       </c>
-      <c r="M11" s="5">
+      <c r="R11">
         <v>731790</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E12" s="4" t="s">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="5">
+      <c r="J12" s="9">
         <v>66313</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E13" s="4" t="s">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I13" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="5">
+      <c r="J13" s="9">
         <v>51339</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E14" s="4" t="s">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="5">
+      <c r="J14" s="9">
         <v>46723</v>
       </c>
-      <c r="K14" t="s">
+      <c r="Q14" t="s">
         <v>61</v>
       </c>
-      <c r="L14">
-        <f>AVERAGE(J5:L10)</f>
+      <c r="R14">
+        <f>AVERAGE(O5:Q10)</f>
         <v>40655</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E15" s="4" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F15" s="5">
+      <c r="J15" s="9">
         <v>45441</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="E16" s="4" t="s">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="I16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="5">
+      <c r="J16" s="9">
         <v>731790</v>
       </c>
     </row>
-    <row r="17" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="J17" t="s">
+    <row r="17" spans="9:18" x14ac:dyDescent="0.3">
+      <c r="P17" t="s">
         <v>62</v>
       </c>
-      <c r="K17" t="s">
+      <c r="Q17" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="5">
+      <c r="R17">
         <v>138661</v>
       </c>
     </row>
-    <row r="18" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="J18" t="s">
+    <row r="18" spans="9:18" x14ac:dyDescent="0.3">
+      <c r="P18" t="s">
         <v>63</v>
       </c>
-      <c r="K18" t="s">
+      <c r="Q18" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="5">
+      <c r="R18">
         <v>103790</v>
       </c>
     </row>
-    <row r="19" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E19" s="4" t="s">
+    <row r="19" spans="9:18" x14ac:dyDescent="0.3">
+      <c r="I19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F19" t="s">
+      <c r="J19" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="6">
+      <c r="K19" s="5">
         <v>96241</v>
       </c>
-      <c r="J19" t="s">
+      <c r="P19" t="s">
         <v>64</v>
       </c>
-      <c r="K19" t="s">
+      <c r="Q19" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="5">
+      <c r="R19">
         <v>55703</v>
       </c>
     </row>
-    <row r="20" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E20" s="4" t="s">
+    <row r="20" spans="9:18" x14ac:dyDescent="0.3">
+      <c r="I20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="10">
+        <v>45441</v>
+      </c>
+      <c r="P20" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>67</v>
+      </c>
+      <c r="R20">
+        <v>27826</v>
+      </c>
+    </row>
+    <row r="21" spans="9:18" x14ac:dyDescent="0.3">
+      <c r="I21" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F20" t="s">
+      <c r="J21" t="s">
         <v>59</v>
       </c>
-      <c r="J20" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" t="s">
-        <v>67</v>
-      </c>
-      <c r="L20" s="5">
-        <v>27826</v>
-      </c>
-    </row>
-    <row r="21" spans="5:12" x14ac:dyDescent="0.3">
-      <c r="E21" s="4" t="s">
+    </row>
+    <row r="22" spans="9:18" x14ac:dyDescent="0.3">
+      <c r="I22" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="F21" t="s">
+      <c r="J22" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I2:M2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="N2:R2"/>
   </mergeCells>
-  <conditionalFormatting pivot="1" sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15">
-    <cfRule type="cellIs" dxfId="26" priority="27" operator="greaterThan">
+  <conditionalFormatting pivot="1" sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15">
+    <cfRule type="cellIs" dxfId="58" priority="32" operator="greaterThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15">
-    <cfRule type="cellIs" dxfId="25" priority="26" operator="lessThan">
+  <conditionalFormatting pivot="1" sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15">
+    <cfRule type="cellIs" dxfId="57" priority="31" operator="lessThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15">
-    <cfRule type="cellIs" dxfId="24" priority="25" operator="greaterThan">
+  <conditionalFormatting pivot="1" sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15">
+    <cfRule type="cellIs" dxfId="56" priority="30" operator="greaterThan">
       <formula>90000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="cellIs" dxfId="23" priority="24" operator="greaterThan">
+  <conditionalFormatting sqref="K19">
+    <cfRule type="cellIs" dxfId="55" priority="29" operator="greaterThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="cellIs" dxfId="22" priority="23" operator="lessThan">
+  <conditionalFormatting sqref="K19">
+    <cfRule type="cellIs" dxfId="54" priority="28" operator="lessThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
-    <cfRule type="cellIs" dxfId="21" priority="22" operator="greaterThan">
+  <conditionalFormatting sqref="K19">
+    <cfRule type="cellIs" dxfId="53" priority="27" operator="greaterThan">
       <formula>90000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="J5:L10">
-    <cfRule type="cellIs" dxfId="20" priority="21" operator="greaterThan">
+  <conditionalFormatting pivot="1" sqref="O5:Q10">
+    <cfRule type="cellIs" dxfId="52" priority="26" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="J5:L10">
-    <cfRule type="cellIs" dxfId="19" priority="20" operator="between">
+  <conditionalFormatting pivot="1" sqref="O5:Q10">
+    <cfRule type="cellIs" dxfId="51" priority="25" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="J5:L10">
-    <cfRule type="cellIs" dxfId="18" priority="19" operator="lessThan">
+  <conditionalFormatting pivot="1" sqref="O5:Q10">
+    <cfRule type="cellIs" dxfId="50" priority="24" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="J5:L10">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="between">
+  <conditionalFormatting pivot="1" sqref="O5:Q10">
+    <cfRule type="cellIs" dxfId="49" priority="23" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="J5:L10">
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
+  <conditionalFormatting pivot="1" sqref="O5:Q10">
+    <cfRule type="cellIs" dxfId="48" priority="22" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="J5:L10">
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="greaterThan">
+  <conditionalFormatting pivot="1" sqref="O5:Q10">
+    <cfRule type="cellIs" dxfId="47" priority="21" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting pivot="1" sqref="J5:L10">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="greaterThan">
+  <conditionalFormatting pivot="1" sqref="O5:Q10">
+    <cfRule type="cellIs" dxfId="46" priority="20" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="greaterThan">
+  <conditionalFormatting sqref="R19">
+    <cfRule type="cellIs" dxfId="45" priority="19" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="between">
+  <conditionalFormatting sqref="R19">
+    <cfRule type="cellIs" dxfId="44" priority="18" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="lessThan">
+  <conditionalFormatting sqref="R19">
+    <cfRule type="cellIs" dxfId="43" priority="17" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="between">
+  <conditionalFormatting sqref="R19">
+    <cfRule type="cellIs" dxfId="42" priority="16" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
+  <conditionalFormatting sqref="R19">
+    <cfRule type="cellIs" dxfId="41" priority="15" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="greaterThan">
+  <conditionalFormatting sqref="R19">
+    <cfRule type="cellIs" dxfId="40" priority="14" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L19">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="greaterThan">
+  <conditionalFormatting sqref="R19">
+    <cfRule type="cellIs" dxfId="39" priority="13" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
+  <conditionalFormatting sqref="R20">
+    <cfRule type="cellIs" dxfId="38" priority="12" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="between">
+  <conditionalFormatting sqref="R20">
+    <cfRule type="cellIs" dxfId="37" priority="11" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+  <conditionalFormatting sqref="R20">
+    <cfRule type="cellIs" dxfId="36" priority="10" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="between">
+  <conditionalFormatting sqref="R20">
+    <cfRule type="cellIs" dxfId="35" priority="9" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="R20">
+    <cfRule type="cellIs" dxfId="34" priority="8" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+  <conditionalFormatting sqref="R20">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="R20">
+    <cfRule type="cellIs" dxfId="32" priority="6" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="J15">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="lessThan">
+      <formula>45450</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="greaterThan">
+      <formula>60000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+      <formula>60000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
+      <formula>90000</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>45450</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
--- a/Data/Cleaned/Aster Retail Holdings Pivot.xlsx
+++ b/Data/Cleaned/Aster Retail Holdings Pivot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\Infotact-Solution-Project-1\Data\Cleaned\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD446D4-3908-4599-B1BD-1B2B77EBDD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D32B3AC-D13F-43FB-A5EC-E124A87EF1AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33854,6 +33854,7 @@
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.109375" bestFit="1" customWidth="1"/>
@@ -34251,143 +34252,143 @@
     <mergeCell ref="N2:R2"/>
   </mergeCells>
   <conditionalFormatting pivot="1" sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15">
-    <cfRule type="cellIs" dxfId="58" priority="32" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="32" operator="greaterThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15">
-    <cfRule type="cellIs" dxfId="57" priority="31" operator="lessThan">
+    <cfRule type="cellIs" dxfId="30" priority="31" operator="lessThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15">
-    <cfRule type="cellIs" dxfId="56" priority="30" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="30" operator="greaterThan">
       <formula>90000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="cellIs" dxfId="55" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="29" operator="greaterThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="cellIs" dxfId="54" priority="28" operator="lessThan">
+    <cfRule type="cellIs" dxfId="27" priority="28" operator="lessThan">
       <formula>60000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K19">
-    <cfRule type="cellIs" dxfId="53" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="27" operator="greaterThan">
       <formula>90000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O5:Q10">
-    <cfRule type="cellIs" dxfId="52" priority="26" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="26" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O5:Q10">
-    <cfRule type="cellIs" dxfId="51" priority="25" operator="between">
+    <cfRule type="cellIs" dxfId="24" priority="25" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O5:Q10">
-    <cfRule type="cellIs" dxfId="50" priority="24" operator="lessThan">
+    <cfRule type="cellIs" dxfId="23" priority="24" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O5:Q10">
-    <cfRule type="cellIs" dxfId="49" priority="23" operator="between">
+    <cfRule type="cellIs" dxfId="22" priority="23" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O5:Q10">
-    <cfRule type="cellIs" dxfId="48" priority="22" operator="lessThan">
+    <cfRule type="cellIs" dxfId="21" priority="22" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O5:Q10">
-    <cfRule type="cellIs" dxfId="47" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="21" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting pivot="1" sqref="O5:Q10">
-    <cfRule type="cellIs" dxfId="46" priority="20" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="45" priority="19" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="19" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="44" priority="18" operator="between">
+    <cfRule type="cellIs" dxfId="17" priority="18" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="43" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="42" priority="16" operator="between">
+    <cfRule type="cellIs" dxfId="15" priority="16" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="41" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="14" priority="15" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="40" priority="14" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R19">
-    <cfRule type="cellIs" dxfId="39" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R20">
-    <cfRule type="cellIs" dxfId="38" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="11" priority="12" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R20">
-    <cfRule type="cellIs" dxfId="37" priority="11" operator="between">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R20">
-    <cfRule type="cellIs" dxfId="36" priority="10" operator="lessThan">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R20">
-    <cfRule type="cellIs" dxfId="35" priority="9" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="between">
       <formula>30000</formula>
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R20">
-    <cfRule type="cellIs" dxfId="34" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThan">
       <formula>30000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R20">
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R20">
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="greaterThan">
       <formula>40655</formula>
     </cfRule>
   </conditionalFormatting>
